--- a/www/download/IND.abstract_labour.empe.s.mv.rpPE.xlsx
+++ b/www/download/IND.abstract_labour.empe.s.mv.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>34737.315</t>
+          <t>34737315282.9885</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35239.875</t>
+          <t>35239875058.4274</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36197.57</t>
+          <t>36197569913.5118</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39652.663</t>
+          <t>39652663205.0728</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>41964.21</t>
+          <t>41964209530.5196</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>45381.777</t>
+          <t>45381777140.7729</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>46189.291</t>
+          <t>46189290621.8234</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47960.912</t>
+          <t>47960912350.8154</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>45696.04</t>
+          <t>45696039979.137</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>49119.436</t>
+          <t>49119436299.0018</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>49943.012</t>
+          <t>49943011958.2955</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>49762.362</t>
+          <t>49762362496.032</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>48158.073</t>
+          <t>48158072743.202</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50040.873</t>
+          <t>50040872997.8552</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>53317.34</t>
+          <t>53317339803.2315</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15623.872</t>
+          <t>15623871971.9642</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15576.186</t>
+          <t>15576186246.8492</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16063.824</t>
+          <t>16063823781.5069</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17198.128</t>
+          <t>17198127818.217</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18256.711</t>
+          <t>18256711462.3324</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>19371.838</t>
+          <t>19371837831.1657</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19806.628</t>
+          <t>19806627592.6281</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19595.149</t>
+          <t>19595149042.0101</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>17943.86</t>
+          <t>17943859585.2951</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19738.815</t>
+          <t>19738815067.6526</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>19231.109</t>
+          <t>19231108643.876</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>18734.263</t>
+          <t>18734262619.0501</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>17856.873</t>
+          <t>17856872761.8574</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>17549.807</t>
+          <t>17549807377.7268</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>17492.118</t>
+          <t>17492117911.9232</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13367.193</t>
+          <t>13367192863.3488</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13423.096</t>
+          <t>13423096394.1322</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13891.33</t>
+          <t>13891330458.4145</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14999.552</t>
+          <t>14999552110.1915</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15809.474</t>
+          <t>15809474030.0206</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17233.324</t>
+          <t>17233323650.4042</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17810.475</t>
+          <t>17810475092.7822</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17725.474</t>
+          <t>17725473755.6914</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>16294.393</t>
+          <t>16294392574.1807</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17712.274</t>
+          <t>17712273565.8871</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17701.569</t>
+          <t>17701569480.7877</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>17592.349</t>
+          <t>17592348655.4067</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>16932.159</t>
+          <t>16932159075.1315</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>17163.928</t>
+          <t>17163927707.7937</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>17222.04</t>
+          <t>17222040274.4616</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9601.423</t>
+          <t>9601423012.65887</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9772.577</t>
+          <t>9772577433.8975</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9155.859</t>
+          <t>9155859332.37009</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8512.92</t>
+          <t>8512919768.11852</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8569.538</t>
+          <t>8569538059.91666</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8326.589</t>
+          <t>8326588660.07736</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8311.037</t>
+          <t>8311037047.95092</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8258.863</t>
+          <t>8258863341.79833</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8373.695</t>
+          <t>8373695363.92926</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9370.141</t>
+          <t>9370141225.06901</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>9532.143</t>
+          <t>9532143381.07338</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9769.731</t>
+          <t>9769731078.4456</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>9800.095</t>
+          <t>9800095160.96926</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>9927.043</t>
+          <t>9927043368.11976</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>9980.155</t>
+          <t>9980155287.01176</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>255004.665</t>
+          <t>255004665150.591</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>253073.693</t>
+          <t>253073692959.454</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>263754.837</t>
+          <t>263754836500.683</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>276689.937</t>
+          <t>276689937016.633</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>295353.6</t>
+          <t>295353600141.416</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>324457.983</t>
+          <t>324457983167.389</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>336100.359</t>
+          <t>336100358544</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>351611.333</t>
+          <t>351611333178.269</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>339054.957</t>
+          <t>339054957378.627</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>374988.657</t>
+          <t>374988657027.131</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>382290.622</t>
+          <t>382290621528.043</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>395300.213</t>
+          <t>395300212659.584</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>393602.284</t>
+          <t>393602284486.051</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>395483.923</t>
+          <t>395483923171.865</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>411950.568</t>
+          <t>411950568446.445</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>81621.064</t>
+          <t>81621064066.9509</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>81723.449</t>
+          <t>81723449236.9595</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83719.841</t>
+          <t>83719841306.6844</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>90147.36</t>
+          <t>90147360273.8719</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>95627.471</t>
+          <t>95627470584.2379</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>103099.205</t>
+          <t>103099205345</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>105519.979</t>
+          <t>105519978778.789</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>106104.906</t>
+          <t>106104906174.883</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>98433.63</t>
+          <t>98433629677.4317</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>106806.047</t>
+          <t>106806046799.536</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>106536.147</t>
+          <t>106536147247.658</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>105875.947</t>
+          <t>105875947089.947</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>101705.547</t>
+          <t>101705546959.529</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>99158.989</t>
+          <t>99158989012.424</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>97739.026</t>
+          <t>97739025844.4015</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>748815.085</t>
+          <t>748815085210.642</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>782797.106</t>
+          <t>782797106092.973</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>820007.446</t>
+          <t>820007446486.443</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>871524.957</t>
+          <t>871524956942.309</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>913212.934</t>
+          <t>913212934030.54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>989369.144</t>
+          <t>989369143843.882</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1108842.818</t>
+          <t>1108842817961.46</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1195904.887</t>
+          <t>1195904887466.93</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1188560.916</t>
+          <t>1188560915706.68</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1293878.711</t>
+          <t>1293878711322</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1337355.596</t>
+          <t>1337355595624.64</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1337234.298</t>
+          <t>1337234297583.67</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1320086.295</t>
+          <t>1320086295382.48</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1361114.839</t>
+          <t>1361114838762.4</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1424857.722</t>
+          <t>1424857721862.12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1460.903</t>
+          <t>1460902785.11247</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1482.407</t>
+          <t>1482406531.00876</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1478.152</t>
+          <t>1478152424.3377</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1534.288</t>
+          <t>1534288491.79434</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1633.083</t>
+          <t>1633082847.97895</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1758.976</t>
+          <t>1758975797.03712</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1844.687</t>
+          <t>1844686572.44164</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1893.952</t>
+          <t>1893952098.86209</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1775.693</t>
+          <t>1775692821.52584</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1880.914</t>
+          <t>1880914389.42031</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1882.883</t>
+          <t>1882882689.5124</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1958.301</t>
+          <t>1958301143.90031</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1974.027</t>
+          <t>1974026520.50223</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2016.937</t>
+          <t>2016937073.30633</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2035.683</t>
+          <t>2035682517.27597</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29388.021</t>
+          <t>29388020739.8717</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28952.079</t>
+          <t>28952078978.2506</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28985.272</t>
+          <t>28985272189.6025</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29679.049</t>
+          <t>29679049304.0984</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29945.551</t>
+          <t>29945551117.4698</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31113.954</t>
+          <t>31113953778.3986</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29971.905</t>
+          <t>29971904592.2729</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29311.12</t>
+          <t>29311120248.2703</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26120.86</t>
+          <t>26120859567.6224</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28224.449</t>
+          <t>28224448518.1751</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>28579.288</t>
+          <t>28579287604.2458</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>28331.435</t>
+          <t>28331434886.4712</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>27221.825</t>
+          <t>27221824951.0157</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>26788.082</t>
+          <t>26788081836.9865</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>26965.281</t>
+          <t>26965280655.8938</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>182480.581</t>
+          <t>182480581290.231</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>176843.196</t>
+          <t>176843195612.679</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>175982.538</t>
+          <t>175982538475.848</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>191097.101</t>
+          <t>191097100686.816</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>196728.36</t>
+          <t>196728359933.115</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>204476.988</t>
+          <t>204476987903.828</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>205422.025</t>
+          <t>205422025288.841</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>202231.564</t>
+          <t>202231563915.725</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>185153.446</t>
+          <t>185153446421.617</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>197988.75</t>
+          <t>197988749621.6</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>188486.387</t>
+          <t>188486387014.472</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>182295.812</t>
+          <t>182295812155.398</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>174655.214</t>
+          <t>174655214386.913</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>171325.55</t>
+          <t>171325549607.848</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>170661.511</t>
+          <t>170661511134.474</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13017.73</t>
+          <t>13017729628.7391</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13078.841</t>
+          <t>13078840672.4307</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13809.795</t>
+          <t>13809794853.8787</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15039.185</t>
+          <t>15039185361.1377</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15887.719</t>
+          <t>15887719176.4931</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16828.466</t>
+          <t>16828466331.1238</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17334.615</t>
+          <t>17334615304.6527</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17273.437</t>
+          <t>17273437250.3819</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15790.441</t>
+          <t>15790441328.8841</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16683.866</t>
+          <t>16683866468.0874</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16668.871</t>
+          <t>16668871039.2134</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>16758.329</t>
+          <t>16758329213.7852</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>15134.574</t>
+          <t>15134573723.3001</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>15220.507</t>
+          <t>15220506946.1131</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14672.96</t>
+          <t>14672960465.9542</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>49865.902</t>
+          <t>49865901931.0544</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53164.351</t>
+          <t>53164350787.4588</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>57528.761</t>
+          <t>57528760625.6883</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>64973.279</t>
+          <t>64973279148.8834</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>71802.962</t>
+          <t>71802962057.0888</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>83111.401</t>
+          <t>83111400683.8509</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>87961.484</t>
+          <t>87961483876.5729</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>90461.953</t>
+          <t>90461952677.6579</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>86313.638</t>
+          <t>86313637688.6069</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>94565.098</t>
+          <t>94565097516.0246</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>98379.348</t>
+          <t>98379347521.8933</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>99949.984</t>
+          <t>99949983510.4014</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>96927.61</t>
+          <t>96927610061.803</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>94332.004</t>
+          <t>94332004236.6846</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>92410.69</t>
+          <t>92410689826.2218</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4742.823</t>
+          <t>4742822838.31295</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4566.342</t>
+          <t>4566342297.15325</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4517.736</t>
+          <t>4517735542.58191</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4560.422</t>
+          <t>4560421874.00839</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4458.384</t>
+          <t>4458383820.8262</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4559.613</t>
+          <t>4559613219.04916</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4750.921</t>
+          <t>4750921139.61547</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4815.271</t>
+          <t>4815271016.33536</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4369.354</t>
+          <t>4369354412.16644</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4652.849</t>
+          <t>4652848875.46938</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4900.767</t>
+          <t>4900767246.78344</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4984.88</t>
+          <t>4984879805.47753</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4651.813</t>
+          <t>4651812594.81165</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>4445.589</t>
+          <t>4445589469.7718</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3932.909</t>
+          <t>3932908926.57838</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11473.674</t>
+          <t>11473673553.6589</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11628.34</t>
+          <t>11628339975.357</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12283.526</t>
+          <t>12283525586.7794</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13237.36</t>
+          <t>13237360061.1339</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13984.187</t>
+          <t>13984186818.6123</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14865.893</t>
+          <t>14865892883.926</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15297.467</t>
+          <t>15297466633.512</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>15457.845</t>
+          <t>15457844592.6031</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>14253.691</t>
+          <t>14253691111.7392</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>15220.345</t>
+          <t>15220345414.4562</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>15097.27</t>
+          <t>15097270160.99</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>14957.513</t>
+          <t>14957513026.8136</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>14453.928</t>
+          <t>14453928017.0377</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>14097.302</t>
+          <t>14097301798.5163</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>13825.826</t>
+          <t>13825825858.35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>103239.059</t>
+          <t>103239059196.444</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>104677.631</t>
+          <t>104677630751.929</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>108164.321</t>
+          <t>108164320984.239</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>117237.559</t>
+          <t>117237559258.326</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>125708.926</t>
+          <t>125708925853.514</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>133414.984</t>
+          <t>133414984263.84</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>137492.283</t>
+          <t>137492283359.902</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>135017.145</t>
+          <t>135017144975.005</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>123117.953</t>
+          <t>123117953076.829</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>132660.995</t>
+          <t>132660995215.755</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>132479.847</t>
+          <t>132479847396.438</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>130064.618</t>
+          <t>130064618336.506</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>126800.687</t>
+          <t>126800687095.224</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>124162.263</t>
+          <t>124162262930.457</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>126314.929</t>
+          <t>126314928870.756</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>129110.664</t>
+          <t>129110663922.537</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>130671.657</t>
+          <t>130671657382.997</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>139667.56</t>
+          <t>139667559504.747</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>152462.381</t>
+          <t>152462381384.304</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>161881.646</t>
+          <t>161881645766.051</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>173717.9</t>
+          <t>173717899726.78</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>177836.086</t>
+          <t>177836085550.94</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>178538.256</t>
+          <t>178538256389.355</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>162600.972</t>
+          <t>162600972120.861</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>172830.114</t>
+          <t>172830114098.272</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>172842.016</t>
+          <t>172842015790.478</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>170611.013</t>
+          <t>170611012868.913</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>162876.353</t>
+          <t>162876352928.241</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>156163.812</t>
+          <t>156163812387.476</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>157582.169</t>
+          <t>157582168878.98</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15397.302</t>
+          <t>15397301781.4623</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15304.687</t>
+          <t>15304687464.7664</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15386.067</t>
+          <t>15386067265.3278</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17398.431</t>
+          <t>17398430903.7093</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18474.811</t>
+          <t>18474811497.3112</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>19596.742</t>
+          <t>19596741923.8707</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20018.076</t>
+          <t>20018075723.0852</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21002.283</t>
+          <t>21002283056.1216</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19705.746</t>
+          <t>19705745787.3932</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>22195.885</t>
+          <t>22195885295.6666</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>21911.612</t>
+          <t>21911611784.1305</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>23157.31</t>
+          <t>23157309705.9274</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>22145.905</t>
+          <t>22145905059.5746</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>21614.992</t>
+          <t>21614991559.6651</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>20805.081</t>
+          <t>20805081394.0191</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22731.721</t>
+          <t>22731720704.9441</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22030.744</t>
+          <t>22030744009.3439</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22491.797</t>
+          <t>22491797411.7702</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>24338.213</t>
+          <t>24338212935.8493</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>26731.406</t>
+          <t>26731405792.1697</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>26873.054</t>
+          <t>26873054033.5049</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27609.929</t>
+          <t>27609928901.4934</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>27756.416</t>
+          <t>27756416103.1385</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25764.053</t>
+          <t>25764053291.276</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>27569.743</t>
+          <t>27569743183.8546</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>27433.205</t>
+          <t>27433205188.7449</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>27148.734</t>
+          <t>27148733540.643</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>25584.053</t>
+          <t>25584052793.7419</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>24701.212</t>
+          <t>24701212170.2871</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>24541.228</t>
+          <t>24541227517.6684</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>100826.834</t>
+          <t>100826833946.367</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>109449.485</t>
+          <t>109449484883.75</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>115514.695</t>
+          <t>115514694782.307</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>127923.878</t>
+          <t>127923877833.784</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>153930.732</t>
+          <t>153930732055.04</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>152894.991</t>
+          <t>152894991275.251</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>155515.24</t>
+          <t>155515240415.988</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>160523.091</t>
+          <t>160523091153.07</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>148208.519</t>
+          <t>148208518522.786</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>164103.839</t>
+          <t>164103838926.663</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>139379.759</t>
+          <t>139379758553.8</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>136199.132</t>
+          <t>136199132047.261</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>128513.274</t>
+          <t>128513273536.214</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>126683.787</t>
+          <t>126683786580.251</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>133079.264</t>
+          <t>133079264290.257</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>822121.745</t>
+          <t>822121744585.448</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>845671.406</t>
+          <t>845671405997.054</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>871129.734</t>
+          <t>871129734099.705</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>918719.259</t>
+          <t>918719258534.658</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>944917.562</t>
+          <t>944917562128.169</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1021875.105</t>
+          <t>1021875104895.95</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1073534.899</t>
+          <t>1073534899476.66</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1072154.081</t>
+          <t>1072154081103.33</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1051850.205</t>
+          <t>1051850204833.81</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1120653.549</t>
+          <t>1120653549159.83</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1108696.344</t>
+          <t>1108696343663.3</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1074870.32</t>
+          <t>1074870320465.02</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1004258.953</t>
+          <t>1004258952931.03</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>988039.918</t>
+          <t>988039918370.015</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1009976.092</t>
+          <t>1009976092426.33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6469.497</t>
+          <t>6469496703.48873</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6961.122</t>
+          <t>6961121933.27827</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7368.433</t>
+          <t>7368433107.15357</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>8467.006</t>
+          <t>8467006314.35831</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9355.192</t>
+          <t>9355192188.82149</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>10219.565</t>
+          <t>10219565362.1327</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10726.729</t>
+          <t>10726729472.7813</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11130.454</t>
+          <t>11130454080.719</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>10564.369</t>
+          <t>10564369049.2739</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>11614.478</t>
+          <t>11614477722.1379</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12201.918</t>
+          <t>12201918088.9957</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>12621.534</t>
+          <t>12621533510.7867</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>12286.66</t>
+          <t>12286659628.3921</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>11755.22</t>
+          <t>11755219688.4502</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>11209.743</t>
+          <t>11209743381.1113</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>62381.857</t>
+          <t>62381857498.0918</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>64268.06</t>
+          <t>64268060322.3451</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>66567.518</t>
+          <t>66567517547.447</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>72608.846</t>
+          <t>72608845764.3198</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>77612.088</t>
+          <t>77612088411.8936</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>83620.582</t>
+          <t>83620582307.6283</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>84193.71</t>
+          <t>84193709722.8071</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>85788.109</t>
+          <t>85788109112.2648</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>81607.547</t>
+          <t>81607547325.1193</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>86664.429</t>
+          <t>86664429410.2511</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>88332.309</t>
+          <t>88332309281.9738</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>89332.8</t>
+          <t>89332799606.0858</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>86971.798</t>
+          <t>86971798112.8476</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>86989.027</t>
+          <t>86989026819.0222</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>85307.464</t>
+          <t>85307464475.9604</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>374610.37</t>
+          <t>374610369793.394</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>378353.47</t>
+          <t>378353469506.765</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>384302.077</t>
+          <t>384302077037.881</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>402208.643</t>
+          <t>402208643010.184</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>409100.521</t>
+          <t>409100521215.56</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>436467.761</t>
+          <t>436467761121.931</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>441875.634</t>
+          <t>441875633772.383</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>433617.38</t>
+          <t>433617380324.117</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>401325.904</t>
+          <t>401325903894.938</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>425673.128</t>
+          <t>425673128478.541</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>413082.214</t>
+          <t>413082214279.282</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>411343.287</t>
+          <t>411343286727.307</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>386501.195</t>
+          <t>386501195358.656</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>360622.331</t>
+          <t>360622330932.688</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>336745.861</t>
+          <t>336745861489.239</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>126674.121</t>
+          <t>126674121219.288</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>128389.912</t>
+          <t>128389912366.169</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>133102.049</t>
+          <t>133102048752.931</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>134619.128</t>
+          <t>134619127835.993</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>148358.355</t>
+          <t>148358354702.148</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>160388.682</t>
+          <t>160388682303.713</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>167449.713</t>
+          <t>167449713129.073</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>177715.329</t>
+          <t>177715328927.196</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>165543.964</t>
+          <t>165543963623.937</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>187964.298</t>
+          <t>187964298440.361</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>183649.883</t>
+          <t>183649882732.887</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>181453.511</t>
+          <t>181453511258.302</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>168362.857</t>
+          <t>168362856684.248</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>161676.326</t>
+          <t>161676325570.968</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>163523.935</t>
+          <t>163523935270.733</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8651.32</t>
+          <t>8651319849.93638</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8215.552</t>
+          <t>8215551858.09755</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8219.642</t>
+          <t>8219641735.87524</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8820.095</t>
+          <t>8820094574.13348</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8815.327</t>
+          <t>8815327202.93316</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9558.268</t>
+          <t>9558268115.60436</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9214.618</t>
+          <t>9214617580.62424</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9314.577</t>
+          <t>9314576648.69024</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8701.312</t>
+          <t>8701311876.81064</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9589.36</t>
+          <t>9589359757.82547</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10235.099</t>
+          <t>10235098646.1532</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10212.715</t>
+          <t>10212715383.4547</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10224.714</t>
+          <t>10224713822.8084</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10256.635</t>
+          <t>10256635105.2062</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>9626.416</t>
+          <t>9626415861.46445</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>946.998</t>
+          <t>946997775.738425</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>954.957</t>
+          <t>954957012.530299</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1024.941</t>
+          <t>1024940814.06622</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1158.209</t>
+          <t>1158209115.4948</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1309.622</t>
+          <t>1309621737.83331</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1440.867</t>
+          <t>1440866668.56779</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1513.185</t>
+          <t>1513185292.6371</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1545.5</t>
+          <t>1545500001.13713</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1303.985</t>
+          <t>1303984954.56965</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1674.795</t>
+          <t>1674795128.94256</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1729.052</t>
+          <t>1729051933.09476</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1680.807</t>
+          <t>1680806729.53599</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1710.51</t>
+          <t>1710509926.67886</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1751.112</t>
+          <t>1751111641.13905</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1961.846</t>
+          <t>1961845586.69939</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5333.272</t>
+          <t>5333271696.61532</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5273.293</t>
+          <t>5273293169.18271</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5158.499</t>
+          <t>5158499337.35602</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5576.217</t>
+          <t>5576217262.15157</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5731.593</t>
+          <t>5731593136.33327</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5958.467</t>
+          <t>5958466577.46459</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5885.238</t>
+          <t>5885238299.45526</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5903.937</t>
+          <t>5903936683.4661</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5336.041</t>
+          <t>5336041012.04138</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5882.936</t>
+          <t>5882935952.41248</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5930.163</t>
+          <t>5930162919.58579</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5985.887</t>
+          <t>5985887087.21774</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5929.764</t>
+          <t>5929763707.5703</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5741.881</t>
+          <t>5741881287.35978</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5018.924</t>
+          <t>5018924429.58795</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>121821.785</t>
+          <t>121821784965.587</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>126339.143</t>
+          <t>126339142822.645</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>136232.826</t>
+          <t>136232825951.537</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>145170.567</t>
+          <t>145170567069.825</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>154191.75</t>
+          <t>154191749502.039</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>166085.579</t>
+          <t>166085579130.493</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>172372.638</t>
+          <t>172372638336.934</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>174749.142</t>
+          <t>174749142384.621</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>165182.345</t>
+          <t>165182344682.199</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>182868.987</t>
+          <t>182868986502.097</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>186352.196</t>
+          <t>186352196066.964</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>185136.229</t>
+          <t>185136228752.407</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>177656.714</t>
+          <t>177656714270.598</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>183136.461</t>
+          <t>183136461413.897</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>182290.882</t>
+          <t>182290882345.22</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>490.702</t>
+          <t>490702234.807561</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>492.634</t>
+          <t>492634489.533981</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>482.105</t>
+          <t>482104880.744501</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>489.421</t>
+          <t>489420705.578407</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>512.41</t>
+          <t>512409541.847644</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>537.032</t>
+          <t>537032008.572635</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>469.854</t>
+          <t>469854361.45134</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>554.452</t>
+          <t>554451718.609528</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>527.666</t>
+          <t>527666227.816671</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>589.533</t>
+          <t>589532847.680305</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>587.771</t>
+          <t>587770846.955639</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>593.379</t>
+          <t>593379359.17894</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>588.491</t>
+          <t>588490775.999053</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>593.366</t>
+          <t>593366116.942693</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>609.224</t>
+          <t>609224101.700199</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>28099.938</t>
+          <t>28099937592.7357</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>29059.829</t>
+          <t>29059829327.9317</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30906.595</t>
+          <t>30906594669.9889</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>33531.964</t>
+          <t>33531963751.9563</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>37471.115</t>
+          <t>37471114579.7482</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>36907.66</t>
+          <t>36907659866.0959</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>37566.246</t>
+          <t>37566246384.2561</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>38425.061</t>
+          <t>38425060914.0874</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>36309.787</t>
+          <t>36309786917.4296</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>38648.225</t>
+          <t>38648224885.9414</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>38217.186</t>
+          <t>38217185705.0359</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>37769.382</t>
+          <t>37769381899.6325</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>36548.934</t>
+          <t>36548933973.6991</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>35555.084</t>
+          <t>35555084140.2837</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>35633.94</t>
+          <t>35633940045.3233</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>53533.672</t>
+          <t>53533672268.9277</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>52891.332</t>
+          <t>52891331718.1137</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>54245.924</t>
+          <t>54245923570.4397</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>57571.682</t>
+          <t>57571681550.5908</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>60921.836</t>
+          <t>60921835689.4518</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>65384.175</t>
+          <t>65384174583.5549</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>71380.221</t>
+          <t>71380221232.3553</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>69329.993</t>
+          <t>69329992732.2677</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>65059.73</t>
+          <t>65059730404.0822</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>71788.556</t>
+          <t>71788555931.6518</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>73068.366</t>
+          <t>73068366460.6501</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>75102.397</t>
+          <t>75102397180.5956</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>74483.125</t>
+          <t>74483125232.7527</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>73996.154</t>
+          <t>73996153890.3948</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>75666.099</t>
+          <t>75666099066.7561</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12663.005</t>
+          <t>12663004591.6843</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12683.982</t>
+          <t>12683982181.5881</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12433.065</t>
+          <t>12433065175.4331</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12648.977</t>
+          <t>12648976756.721</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13521.486</t>
+          <t>13521485762.485</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14296.768</t>
+          <t>14296767774.3143</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>14651.451</t>
+          <t>14651450872.697</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>14926.547</t>
+          <t>14926547237.4844</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14483.449</t>
+          <t>14483448590.534</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>15992.007</t>
+          <t>15992007464.0784</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16061.311</t>
+          <t>16061311378.6687</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>17127.506</t>
+          <t>17127505782.1605</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>16698.74</t>
+          <t>16698740148.772</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>16596.583</t>
+          <t>16596582590.306</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>16920.483</t>
+          <t>16920482692.6067</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20633.272</t>
+          <t>20633271962.0427</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20919.242</t>
+          <t>20919242003.0331</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18881.911</t>
+          <t>18881910716.9909</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>18365.791</t>
+          <t>18365790819.2756</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21633.405</t>
+          <t>21633404837.8902</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>22271.454</t>
+          <t>22271453795.2367</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>22231.56</t>
+          <t>22231560176.9402</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>23783.716</t>
+          <t>23783716444.7289</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>23007.164</t>
+          <t>23007163906.5362</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>26377.709</t>
+          <t>26377708809.5144</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>25746.863</t>
+          <t>25746863352.8894</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>26441.493</t>
+          <t>26441492636.5774</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>25458.582</t>
+          <t>25458581586.5022</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>25641.472</t>
+          <t>25641471794.1107</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>26900.932</t>
+          <t>26900931706.7631</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>410555.117</t>
+          <t>410555116653.145</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>400576.842</t>
+          <t>400576841510.435</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>397881.719</t>
+          <t>397881718733.923</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>400702.392</t>
+          <t>400702392074.341</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>413590.931</t>
+          <t>413590930911.26</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>434436.866</t>
+          <t>434436866290.052</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>441033.589</t>
+          <t>441033589257.944</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>439171.665</t>
+          <t>439171664536.815</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>400560.444</t>
+          <t>400560443733.551</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>430605.81</t>
+          <t>430605810476.65</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>429825.493</t>
+          <t>429825493314.13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>421000.845</t>
+          <t>421000844906.613</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>400454.874</t>
+          <t>400454873966.32</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>355943.688</t>
+          <t>355943688068.631</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>350163.052</t>
+          <t>350163052186.907</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>12443.488</t>
+          <t>12443488093.7509</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12214.952</t>
+          <t>12214951927.815</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12179.489</t>
+          <t>12179489312.9308</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12583.61</t>
+          <t>12583610305.9194</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>12473.257</t>
+          <t>12473256576.6952</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12759.94</t>
+          <t>12759939951.6044</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12782.895</t>
+          <t>12782894819.7564</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>12386.189</t>
+          <t>12386189350.5088</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>10968.241</t>
+          <t>10968240609.3789</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>11675.754</t>
+          <t>11675754360.2124</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>11949.493</t>
+          <t>11949492889.7943</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>11775.704</t>
+          <t>11775703552.6432</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>11378.328</t>
+          <t>11378327757.0695</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>11083.948</t>
+          <t>11083947787.2351</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>10661.553</t>
+          <t>10661552679.4417</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4490.804</t>
+          <t>4490803826.77233</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4391.045</t>
+          <t>4391044935.35213</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4329.442</t>
+          <t>4329442127.42673</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4554.627</t>
+          <t>4554627306.3088</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4840.055</t>
+          <t>4840054689.64288</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5182.969</t>
+          <t>5182969151.06684</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5043.98</t>
+          <t>5043980107.84093</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>5169.32</t>
+          <t>5169320279.36507</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4907.872</t>
+          <t>4907871578.34825</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5262.994</t>
+          <t>5262994110.58458</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>5233.259</t>
+          <t>5233259092.7755</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>5264.775</t>
+          <t>5264775237.06622</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>5105.611</t>
+          <t>5105610544.81805</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>5040.548</t>
+          <t>5040547968.5841</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>5047.106</t>
+          <t>5047105632.23007</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>21291.211</t>
+          <t>21291211312.1743</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>21196.895</t>
+          <t>21196895417.5624</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>21335.801</t>
+          <t>21335800611.5519</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>22912.492</t>
+          <t>22912492429.0313</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>24423.052</t>
+          <t>24423052414.8472</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>27251.029</t>
+          <t>27251028947.4931</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>28121.148</t>
+          <t>28121147612.2064</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>27637.213</t>
+          <t>27637212569.776</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>25027.504</t>
+          <t>25027504078.9259</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>26807.863</t>
+          <t>26807862913.2994</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>26512.722</t>
+          <t>26512722157.1983</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>26524.605</t>
+          <t>26524604759.3356</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>25948.799</t>
+          <t>25948798782.1485</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>25462.089</t>
+          <t>25462088705.7265</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>24991.649</t>
+          <t>24991649206.6532</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>44519.739</t>
+          <t>44519738638.2847</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>47025.573</t>
+          <t>47025573179.3349</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>48560.646</t>
+          <t>48560645796.9189</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>49708.477</t>
+          <t>49708476951.4049</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>50855.775</t>
+          <t>50855775144.1277</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>56237.541</t>
+          <t>56237541468.3059</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>56582.167</t>
+          <t>56582166726.6671</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>59737.486</t>
+          <t>59737485645.8833</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>57646.58</t>
+          <t>57646580445.5604</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>58525.074</t>
+          <t>58525074219.8692</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>62936.119</t>
+          <t>62936118742.728</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>62714.636</t>
+          <t>62714636200.2833</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>60589.372</t>
+          <t>60589371748.9201</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>60784.489</t>
+          <t>60784489049.7398</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>62202.744</t>
+          <t>62202744336.429</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>45178.657</t>
+          <t>45178657345.1908</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>45572.657</t>
+          <t>45572656827.3104</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>47805.134</t>
+          <t>47805134311.1539</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>51040.885</t>
+          <t>51040885252.2535</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>53910.15</t>
+          <t>53910150318.8306</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>58199.313</t>
+          <t>58199313373.9259</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>56584.147</t>
+          <t>56584146769.6467</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>57756.353</t>
+          <t>57756352929.8515</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>54878.552</t>
+          <t>54878552425.8559</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>60501.412</t>
+          <t>60501412217.5805</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>61804.51</t>
+          <t>61804509794.0945</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>62497.808</t>
+          <t>62497807909.3571</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>61126.214</t>
+          <t>61126213832.8444</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>61433.741</t>
+          <t>61433740960.7313</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>62968.08</t>
+          <t>62968080197.2214</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>873005.702</t>
+          <t>873005702190.613</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>883221.88</t>
+          <t>883221879987.958</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>916111.063</t>
+          <t>916111062790.422</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>998753.086</t>
+          <t>998753086110.278</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1048812.429</t>
+          <t>1048812428738.08</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1119206.808</t>
+          <t>1119206808460.03</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1111705.228</t>
+          <t>1111705228480.11</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1087640.791</t>
+          <t>1087640791199.67</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>988393.727</t>
+          <t>988393727226.814</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1059751.066</t>
+          <t>1059751065590.07</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1056141.689</t>
+          <t>1056141689273.11</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1051216.628</t>
+          <t>1051216628469.57</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>999798.647</t>
+          <t>999798646778.45</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>957842.933</t>
+          <t>957842933081.155</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>931926.066</t>
+          <t>931926066460.326</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1676297.094</t>
+          <t>1676297093531.13</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1737963.31</t>
+          <t>1737963310334.94</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1807985.839</t>
+          <t>1807985838923.91</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1898193.889</t>
+          <t>1898193888745.62</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1972609.952</t>
+          <t>1972609952133.95</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2148392.432</t>
+          <t>2148392431581.54</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2287189.247</t>
+          <t>2287189246892.46</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2338336.932</t>
+          <t>2338336932149.19</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2301058.294</t>
+          <t>2301058294184.36</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2595256.68</t>
+          <t>2595256679968.34</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2632539.463</t>
+          <t>2632539462778.16</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2685964.295</t>
+          <t>2685964295432.1</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2671086.405</t>
+          <t>2671086405394.53</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2736949.143</t>
+          <t>2736949143311.51</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2861453.312</t>
+          <t>2861453311900.28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6554719.194</t>
+          <t>6554719194206.73</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6696092.832</t>
+          <t>6696092831598.79</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6924845.377</t>
+          <t>6924845377432.51</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7336611.927</t>
+          <t>7336611926618.66</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>7684929.566</t>
+          <t>7684929566139.25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8267131.685</t>
+          <t>8267131685194.43</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>8635743.402</t>
+          <t>8635743401776.44</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>8778218.086</t>
+          <t>8778218085760.7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8401776.538</t>
+          <t>8401776537998.48</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>9184559.573</t>
+          <t>9184559573177.59</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9221464.873</t>
+          <t>9221464873253.5</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>9227316.765</t>
+          <t>9227316765268.86</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>8952249.873</t>
+          <t>8952249873203.25</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>8908883.587</t>
+          <t>8908883587289.65</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>9090191.905</t>
+          <t>9090191905245</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.empe.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
